--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.4766</v>
+        <v>17.35383</v>
       </c>
       <c r="D2" t="n">
-        <v>16.89653</v>
+        <v>16.96114</v>
       </c>
       <c r="E2" t="n">
-        <v>17.45388</v>
+        <v>17.11534</v>
       </c>
       <c r="F2" t="n">
-        <v>43.69816</v>
+        <v>43.72418</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05187</v>
+        <v>0.05257</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9009</v>
+        <v>1.88238</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.70981</v>
+        <v>17.44126</v>
       </c>
       <c r="D3" t="n">
-        <v>17.03244</v>
+        <v>16.68602</v>
       </c>
       <c r="E3" t="n">
-        <v>17.49056</v>
+        <v>17.24408</v>
       </c>
       <c r="F3" t="n">
-        <v>44.08068</v>
+        <v>43.96352</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05292</v>
+        <v>0.05202</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85668</v>
+        <v>1.87153</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.58835</v>
+        <v>16.99727</v>
       </c>
       <c r="D4" t="n">
-        <v>16.93737</v>
+        <v>16.85256</v>
       </c>
       <c r="E4" t="n">
-        <v>16.70999</v>
+        <v>16.90562</v>
       </c>
       <c r="F4" t="n">
-        <v>43.82794</v>
+        <v>44.06742</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05176</v>
+        <v>0.05271</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87434</v>
+        <v>1.88995</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.14431</v>
+        <v>17.1906</v>
       </c>
       <c r="D6" t="n">
-        <v>16.53526</v>
+        <v>16.73318</v>
       </c>
       <c r="E6" t="n">
-        <v>16.7893</v>
+        <v>16.8017</v>
       </c>
       <c r="F6" t="n">
-        <v>22.50235</v>
+        <v>22.23919</v>
       </c>
       <c r="G6" t="n">
-        <v>35.52156</v>
+        <v>35.76902</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.0881</v>
+        <v>16.70144</v>
       </c>
       <c r="D7" t="n">
-        <v>16.36802</v>
+        <v>16.63918</v>
       </c>
       <c r="E7" t="n">
-        <v>16.49459</v>
+        <v>16.65952</v>
       </c>
       <c r="F7" t="n">
-        <v>22.43734</v>
+        <v>22.11757</v>
       </c>
       <c r="G7" t="n">
-        <v>34.47254</v>
+        <v>35.59112</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.09943</v>
+        <v>17.11155</v>
       </c>
       <c r="D8" t="n">
-        <v>16.52161</v>
+        <v>16.37585</v>
       </c>
       <c r="E8" t="n">
-        <v>16.93804</v>
+        <v>16.77417</v>
       </c>
       <c r="F8" t="n">
-        <v>22.48137</v>
+        <v>22.56976</v>
       </c>
       <c r="G8" t="n">
-        <v>34.65031</v>
+        <v>35.19947</v>
       </c>
     </row>
   </sheetData>
